--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_4.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_4.xlsx
@@ -463,31 +463,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[7, 0, 0, 5, 8]</t>
+          <t>[7, 6, 0, 5, 3]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9635342203530427</v>
+        <v>0.975106926759729</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9635342203530427</v>
+        <v>0.975106926759729</v>
       </c>
       <c r="E2" t="n">
-        <v>66.28</v>
+        <v>96.25999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>64.28999999999999</v>
+        <v>77.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[9, 8, 5, 2, 6]</t>
+          <t>[6, 1, 9, 8, 9]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -496,166 +496,166 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.952472971059964</v>
+        <v>0.9416661066096078</v>
       </c>
       <c r="D3" t="n">
-        <v>0.952472971059964</v>
+        <v>0.9416661066096078</v>
       </c>
       <c r="E3" t="n">
-        <v>84.33</v>
+        <v>83.2</v>
       </c>
       <c r="F3" t="n">
-        <v>63.56</v>
+        <v>65.46000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[9, 3, 7, 3, 3]</t>
+          <t>[7, 6, 9, 3, 5]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9702440288099959</v>
+        <v>0.9415751244580626</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9702440288099959</v>
+        <v>0.9415751244580626</v>
       </c>
       <c r="E4" t="n">
-        <v>92.75</v>
+        <v>73.08</v>
       </c>
       <c r="F4" t="n">
-        <v>79.83</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[6, 7, 1, 2, 8]</t>
+          <t>[3, 9, 6, 3, 9]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9654204062468135</v>
+        <v>0.9498710278920997</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9654204062468135</v>
+        <v>0.9498710278920997</v>
       </c>
       <c r="E5" t="n">
-        <v>93.22999999999999</v>
+        <v>74.39</v>
       </c>
       <c r="F5" t="n">
-        <v>74.17</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[3, 1, 6, 3, 3]</t>
+          <t>[5, 1, 6, 8, 0]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9811627608102969</v>
+        <v>0.9537571446393924</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9811627608102969</v>
+        <v>0.9537571446393924</v>
       </c>
       <c r="E6" t="n">
-        <v>87.26999999999998</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>73.83</v>
+        <v>65.28999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[8, 6, 3, 3, 3]</t>
+          <t>[3, 5, 0, 7, 2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9754198433556314</v>
+        <v>0.9599901304367143</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9754198433556314</v>
+        <v>0.9599901304367143</v>
       </c>
       <c r="E7" t="n">
-        <v>84.84999999999999</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>72.40000000000001</v>
+        <v>64.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[4, 8, 0, 4, 3]</t>
+          <t>[9, 7, 9, 1, 3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9809367416262459</v>
+        <v>0.9709720718953903</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9809367416262459</v>
+        <v>0.9709720718953903</v>
       </c>
       <c r="E8" t="n">
-        <v>97.53</v>
+        <v>92.61999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>77.58</v>
+        <v>73.71000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[6, 3, 3, 1, 9]</t>
+          <t>[3, 3, 0, 4, 4]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9776183834370616</v>
+        <v>0.9680336932471978</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9776183834370616</v>
+        <v>0.9680336932471978</v>
       </c>
       <c r="E9" t="n">
-        <v>96.44</v>
+        <v>93.28999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>73.45</v>
+        <v>61.22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[7, 9, 5, 5, 5]</t>
+          <t>[4, 1, 9, 6, 2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -664,118 +664,118 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9494080682504112</v>
+        <v>0.9518896481079251</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9494080682504112</v>
+        <v>0.9518896481079251</v>
       </c>
       <c r="E10" t="n">
-        <v>74.59999999999999</v>
+        <v>94.64000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>64.59999999999999</v>
+        <v>67.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[0, 6, 5, 5, 5]</t>
+          <t>[3, 1, 7, 3, 1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9745239013098085</v>
+        <v>0.9812552647090406</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9745239013098085</v>
+        <v>0.9812552647090406</v>
       </c>
       <c r="E11" t="n">
-        <v>80.03999999999999</v>
+        <v>88.75999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>74.65000000000001</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[4, 5, 8, 8, 6]</t>
+          <t>[1, 3, 5, 5, 1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9743903428565864</v>
+        <v>0.9787671573780781</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9743903428565864</v>
+        <v>0.9787671573780781</v>
       </c>
       <c r="E12" t="n">
-        <v>89.56</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>70.91</v>
+        <v>73.55999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[8, 6, 0, 5, 0]</t>
+          <t>[5, 3, 3, 2, 3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9771801782858164</v>
+        <v>0.9664389854037523</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9771801782858164</v>
+        <v>0.9664389854037523</v>
       </c>
       <c r="E13" t="n">
-        <v>79.84</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>74.09</v>
+        <v>56.24999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[8, 6, 5, 1, 5]</t>
+          <t>[3, 5, 9, 3, 6]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.980738542148582</v>
+        <v>0.9587634082391036</v>
       </c>
       <c r="D14" t="n">
-        <v>0.980738542148582</v>
+        <v>0.9587634082391036</v>
       </c>
       <c r="E14" t="n">
-        <v>98.53</v>
+        <v>90.47999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>78.78999999999999</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[0, 6, 1, 1, 3]</t>
+          <t>[0, 7, 3, 8, 3]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -784,70 +784,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9833105297721602</v>
+        <v>0.9799583612070413</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9833105297721602</v>
+        <v>0.9799583612070413</v>
       </c>
       <c r="E15" t="n">
-        <v>86.97</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>73.53999999999999</v>
+        <v>78.46000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[5, 1, 2, 0, 9]</t>
+          <t>[3, 9, 0, 2, 7]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9792799332803052</v>
+        <v>0.961187305242435</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9792799332803052</v>
+        <v>0.961187305242435</v>
       </c>
       <c r="E16" t="n">
-        <v>99.31999999999999</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>79.43000000000001</v>
+        <v>62.55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[4, 1, 5, 5, 5]</t>
+          <t>[3, 9, 9, 6, 1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9651910264700693</v>
+        <v>0.9606565598091332</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9651910264700693</v>
+        <v>0.9606565598091332</v>
       </c>
       <c r="E17" t="n">
-        <v>92.18000000000001</v>
+        <v>97.38</v>
       </c>
       <c r="F17" t="n">
-        <v>72.90000000000001</v>
+        <v>70.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[3, 7, 4, 0, 5]</t>
+          <t>[8, 5, 6, 1, 0]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -856,70 +856,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9642756506222921</v>
+        <v>0.952000022656175</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9642756506222921</v>
+        <v>0.952000022656175</v>
       </c>
       <c r="E18" t="n">
-        <v>75.05</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>70.03999999999999</v>
+        <v>65.29000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[5, 7, 8, 1, 5]</t>
+          <t>[7, 4, 3, 3, 4]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.97669802198498</v>
+        <v>0.9785315772082521</v>
       </c>
       <c r="D19" t="n">
-        <v>0.97669802198498</v>
+        <v>0.9785315772082521</v>
       </c>
       <c r="E19" t="n">
-        <v>84.43000000000001</v>
+        <v>95.81</v>
       </c>
       <c r="F19" t="n">
-        <v>70.52000000000001</v>
+        <v>77.10999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[4, 8, 8, 3, 3]</t>
+          <t>[8, 0, 8, 3, 9]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9753558868754891</v>
+        <v>0.9562273261922011</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9753558868754891</v>
+        <v>0.9562273261922011</v>
       </c>
       <c r="E20" t="n">
-        <v>92.66</v>
+        <v>96.19</v>
       </c>
       <c r="F20" t="n">
-        <v>69.19</v>
+        <v>75.93000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[4, 4, 8, 2, 4]</t>
+          <t>[8, 1, 2, 5, 3]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -928,190 +928,190 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9623380676705393</v>
+        <v>0.9612694208717133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9623380676705393</v>
+        <v>0.9612694208717133</v>
       </c>
       <c r="E21" t="n">
-        <v>99.37</v>
+        <v>81.16000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>74.20999999999999</v>
+        <v>64.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[6, 5, 6, 9, 3]</t>
+          <t>[7, 1, 0, 8, 1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9692242229268089</v>
+        <v>0.9592511090047804</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9692242229268089</v>
+        <v>0.9592511090047804</v>
       </c>
       <c r="E22" t="n">
-        <v>88.72999999999999</v>
+        <v>88.14</v>
       </c>
       <c r="F22" t="n">
-        <v>76.88</v>
+        <v>65.75999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[5, 0, 5, 3, 8]</t>
+          <t>[7, 0, 7, 7, 3]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9806013586722327</v>
+        <v>0.9486325281782868</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9806013586722327</v>
+        <v>0.9486325281782868</v>
       </c>
       <c r="E23" t="n">
-        <v>82.86999999999999</v>
+        <v>71.52</v>
       </c>
       <c r="F23" t="n">
-        <v>69.71000000000001</v>
+        <v>69.60999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[8, 8, 6, 0, 6]</t>
+          <t>[4, 9, 6, 3, 2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9720590143221088</v>
+        <v>0.9502768678210034</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9720590143221088</v>
+        <v>0.9502768678210034</v>
       </c>
       <c r="E24" t="n">
-        <v>81.36000000000001</v>
+        <v>87.72999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>67.64000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[0, 1, 8, 8, 5]</t>
+          <t>[4, 0, 8, 3, 8]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9779273778765761</v>
+        <v>0.9594546216845895</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9779273778765761</v>
+        <v>0.9594546216845895</v>
       </c>
       <c r="E25" t="n">
-        <v>84.01999999999998</v>
+        <v>86.88</v>
       </c>
       <c r="F25" t="n">
-        <v>68.28</v>
+        <v>67.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[6, 3, 6, 1, 4]</t>
+          <t>[0, 8, 4, 7, 2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9806464697576559</v>
+        <v>0.9527691959484091</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9806464697576559</v>
+        <v>0.9527691959484091</v>
       </c>
       <c r="E26" t="n">
-        <v>91.67</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>78.44</v>
+        <v>73.20999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[6, 3, 6, 3, 9]</t>
+          <t>[8, 9, 7, 6, 3]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9626194065807101</v>
+        <v>0.9332713353830691</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9626194065807101</v>
+        <v>0.9332713353830691</v>
       </c>
       <c r="E27" t="n">
-        <v>97.36000000000001</v>
+        <v>72.39999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>79.06</v>
+        <v>68.06999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[9, 4, 0, 8, 2]</t>
+          <t>[1, 7, 3, 2, 3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9577952419214714</v>
+        <v>0.981542566387984</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9577952419214714</v>
+        <v>0.981542566387984</v>
       </c>
       <c r="E28" t="n">
-        <v>91.19</v>
+        <v>88.42</v>
       </c>
       <c r="F28" t="n">
-        <v>69.28</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[0, 9, 6, 4, 3]</t>
+          <t>[8, 8, 3, 7, 2]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1120,46 +1120,46 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9587227881472201</v>
+        <v>0.9454720686352347</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9587227881472201</v>
+        <v>0.9454720686352347</v>
       </c>
       <c r="E29" t="n">
-        <v>82.42000000000002</v>
+        <v>73.12</v>
       </c>
       <c r="F29" t="n">
-        <v>69.64</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[3, 8, 5, 3, 9]</t>
+          <t>[3, 8, 3, 7, 6]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9617997965845868</v>
+        <v>0.9651336141160466</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9617997965845868</v>
+        <v>0.9651336141160466</v>
       </c>
       <c r="E30" t="n">
-        <v>98.78</v>
+        <v>81.60000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>73.91</v>
+        <v>74.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[7, 9, 1, 8, 3]</t>
+          <t>[7, 1, 3, 9, 0]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1168,190 +1168,190 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.952612866325652</v>
+        <v>0.9542643176519202</v>
       </c>
       <c r="D31" t="n">
-        <v>0.952612866325652</v>
+        <v>0.9542643176519202</v>
       </c>
       <c r="E31" t="n">
-        <v>78.81</v>
+        <v>82.77</v>
       </c>
       <c r="F31" t="n">
-        <v>62.8</v>
+        <v>59.77</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 6]</t>
+          <t>[3, 7, 9, 6, 2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9732580619856296</v>
+        <v>0.9643043375140654</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9732580619856296</v>
+        <v>0.9643043375140654</v>
       </c>
       <c r="E32" t="n">
-        <v>98.46000000000001</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>73.87</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[0, 3, 3, 7, 2]</t>
+          <t>[3, 2, 6, 5, 9]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9646920967631852</v>
+        <v>0.9739016071261094</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9646920967631852</v>
+        <v>0.9739016071261094</v>
       </c>
       <c r="E33" t="n">
-        <v>78</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>70.22</v>
+        <v>77.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[5, 8, 8, 6, 6]</t>
+          <t>[5, 0, 4, 2, 9]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9710401201757205</v>
+        <v>0.9645226150235721</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9710401201757205</v>
+        <v>0.9645226150235721</v>
       </c>
       <c r="E34" t="n">
-        <v>82.2</v>
+        <v>95.67</v>
       </c>
       <c r="F34" t="n">
-        <v>65.37</v>
+        <v>66.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[6, 9, 8, 3, 0]</t>
+          <t>[6, 9, 3, 2, 9]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9524245023930783</v>
+        <v>0.9723411057098044</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9524245023930783</v>
+        <v>0.9723411057098044</v>
       </c>
       <c r="E35" t="n">
-        <v>75.59999999999999</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>62.56999999999999</v>
+        <v>71.02</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[1, 3, 8, 7, 6]</t>
+          <t>[2, 1, 7, 9, 1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9775691232399633</v>
+        <v>0.9559849036380058</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9775691232399633</v>
+        <v>0.9559849036380058</v>
       </c>
       <c r="E36" t="n">
-        <v>86.11</v>
+        <v>86.58</v>
       </c>
       <c r="F36" t="n">
-        <v>73.95000000000002</v>
+        <v>65.74000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[2, 1, 8, 3, 0]</t>
+          <t>[0, 8, 6, 3, 4]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9670989020105205</v>
+        <v>0.9573292621793645</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9670989020105205</v>
+        <v>0.9573292621793645</v>
       </c>
       <c r="E37" t="n">
-        <v>93.79000000000001</v>
+        <v>89.28999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>75.53</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[6, 1, 6, 3, 6]</t>
+          <t>[3, 3, 3, 8, 4]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9747904717659199</v>
+        <v>0.9609219919007945</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9747904717659199</v>
+        <v>0.9609219919007945</v>
       </c>
       <c r="E38" t="n">
-        <v>87.27</v>
+        <v>75.31</v>
       </c>
       <c r="F38" t="n">
-        <v>72.80000000000001</v>
+        <v>60.45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[5, 1, 7, 9, 0]</t>
+          <t>[7, 1, 2, 7, 0]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1360,22 +1360,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9558984181684357</v>
+        <v>0.9583462973330501</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9558984181684357</v>
+        <v>0.9583462973330501</v>
       </c>
       <c r="E39" t="n">
-        <v>76.52000000000001</v>
+        <v>85.45</v>
       </c>
       <c r="F39" t="n">
-        <v>66.20999999999999</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[5, 3, 9, 7, 9]</t>
+          <t>[8, 9, 5, 5, 2]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1384,70 +1384,70 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9515353294095258</v>
+        <v>0.9440243896321041</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9515353294095258</v>
+        <v>0.9440243896321041</v>
       </c>
       <c r="E40" t="n">
-        <v>82.69</v>
+        <v>80.27</v>
       </c>
       <c r="F40" t="n">
-        <v>68.31</v>
+        <v>69.88</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[0, 1, 7, 3, 1]</t>
+          <t>[9, 0, 7, 6, 0]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9798071506215037</v>
+        <v>0.9457111965943901</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9798071506215037</v>
+        <v>0.9457111965943901</v>
       </c>
       <c r="E41" t="n">
-        <v>88.22999999999999</v>
+        <v>89.84</v>
       </c>
       <c r="F41" t="n">
-        <v>76.12</v>
+        <v>62.95999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[3, 8, 7, 6, 5]</t>
+          <t>[9, 3, 6, 5, 5]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9583531146800417</v>
+        <v>0.9735721945435197</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9583531146800417</v>
+        <v>0.9735721945435197</v>
       </c>
       <c r="E42" t="n">
-        <v>82.24000000000001</v>
+        <v>92.19</v>
       </c>
       <c r="F42" t="n">
-        <v>73.66</v>
+        <v>74.94</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[8, 8, 0, 3, 0]</t>
+          <t>[4, 0, 4, 7, 5]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1456,22 +1456,22 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9602003081200366</v>
+        <v>0.9598759244898446</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9602003081200366</v>
+        <v>0.9598759244898446</v>
       </c>
       <c r="E43" t="n">
-        <v>68.66</v>
+        <v>95.41999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>58.45999999999999</v>
+        <v>72.78999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[7, 8, 5, 6, 4]</t>
+          <t>[3, 9, 7, 1, 9]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1480,70 +1480,70 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9726452642017831</v>
+        <v>0.9709713446832653</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9726452642017831</v>
+        <v>0.9709713446832653</v>
       </c>
       <c r="E44" t="n">
-        <v>87.75</v>
+        <v>96.08999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>79.22</v>
+        <v>73.05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[8, 6, 0, 9, 4]</t>
+          <t>[7, 1, 2, 6, 3]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9758050169751872</v>
+        <v>0.961716347636313</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9758050169751872</v>
+        <v>0.961716347636313</v>
       </c>
       <c r="E45" t="n">
-        <v>94.82000000000001</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>79.56</v>
+        <v>74.94999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[8, 7, 9, 9, 5]</t>
+          <t>[0, 9, 9, 3, 6]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9427072518352847</v>
+        <v>0.9710645205845575</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9427072518352847</v>
+        <v>0.9710645205845575</v>
       </c>
       <c r="E46" t="n">
-        <v>81.91999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="F46" t="n">
-        <v>65.27</v>
+        <v>67.03</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[9, 2, 7, 9, 9]</t>
+          <t>[3, 6, 0, 8, 8]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1552,22 +1552,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.94843675923473</v>
+        <v>0.9534279032517254</v>
       </c>
       <c r="D47" t="n">
-        <v>0.94843675923473</v>
+        <v>0.9534279032517254</v>
       </c>
       <c r="E47" t="n">
-        <v>97.56</v>
+        <v>80.97999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>74.33</v>
+        <v>65.61999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[8, 0, 0, 2, 8]</t>
+          <t>[2, 3, 3, 2, 6]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1576,88 +1576,88 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9783942720530066</v>
+        <v>0.982599379485075</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9783942720530066</v>
+        <v>0.982599379485075</v>
       </c>
       <c r="E48" t="n">
-        <v>89.42</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>75.42</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[8, 5, 6, 1, 4]</t>
+          <t>[3, 1, 8, 3, 6]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.973018779889082</v>
+        <v>0.9751496095024164</v>
       </c>
       <c r="D49" t="n">
-        <v>0.973018779889082</v>
+        <v>0.9751496095024164</v>
       </c>
       <c r="E49" t="n">
-        <v>94.74000000000001</v>
+        <v>95.87</v>
       </c>
       <c r="F49" t="n">
-        <v>71.68000000000001</v>
+        <v>71.59</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[3, 8, 7, 5, 0]</t>
+          <t>[4, 5, 1, 2, 7]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9757077118457853</v>
+        <v>0.9649181884016409</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9757077118457853</v>
+        <v>0.9649181884016409</v>
       </c>
       <c r="E50" t="n">
-        <v>81.94</v>
+        <v>89.02000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>74.40000000000001</v>
+        <v>72.11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[9, 5, 0, 1, 8]</t>
+          <t>[4, 0, 9, 8, 9]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.975513715998414</v>
+        <v>0.9497678731587298</v>
       </c>
       <c r="D51" t="n">
-        <v>0.975513715998414</v>
+        <v>0.9497678731587298</v>
       </c>
       <c r="E51" t="n">
-        <v>91.49999999999999</v>
+        <v>91.86</v>
       </c>
       <c r="F51" t="n">
-        <v>70.86</v>
+        <v>66.5</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_4.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_4.xlsx
@@ -463,1201 +463,1201 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[5, 7, 4, 9, 3]</t>
+          <t>[9, 7, 7, 4, 8]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9317883712498192</v>
+        <v>0.961069264612964</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9317883712498192</v>
+        <v>0.961069264612964</v>
       </c>
       <c r="E2" t="n">
-        <v>91.84</v>
+        <v>94.63000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>73.20999999999999</v>
+        <v>77.06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[8, 3, 5, 3, 6]</t>
+          <t>[8, 0, 9, 6, 9]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9398019684858918</v>
+        <v>0.9603114227836372</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9398019684858918</v>
+        <v>0.9603114227836372</v>
       </c>
       <c r="E3" t="n">
-        <v>90.13999999999999</v>
+        <v>115.23</v>
       </c>
       <c r="F3" t="n">
-        <v>75.19</v>
+        <v>88.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[5, 4, 1, 6, 4]</t>
+          <t>[7, 7, 8, 6, 7]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9496349128568339</v>
+        <v>0.9626052054139339</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9496349128568339</v>
+        <v>0.9626052054139339</v>
       </c>
       <c r="E4" t="n">
-        <v>82.37</v>
+        <v>86.99000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>68.29000000000001</v>
+        <v>73.61999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[6, 6, 1, 0, 2]</t>
+          <t>[1, 7, 3, 7, 6]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9577620834576014</v>
+        <v>0.966918932696361</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9577620834576014</v>
+        <v>0.966918932696361</v>
       </c>
       <c r="E5" t="n">
-        <v>90.14999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="F5" t="n">
-        <v>64.95</v>
+        <v>75.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[4, 5, 2, 7, 9]</t>
+          <t>[6, 4, 7, 0, 8]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9401585102977674</v>
+        <v>0.9895642721316892</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9401585102977674</v>
+        <v>0.9895642721316892</v>
       </c>
       <c r="E6" t="n">
-        <v>91.05000000000001</v>
+        <v>119.99</v>
       </c>
       <c r="F6" t="n">
-        <v>70.97</v>
+        <v>92.96000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[6, 1, 8, 7, 2]</t>
+          <t>[1, 7, 1, 4, 8]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9406672631393728</v>
+        <v>0.9766628971545965</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9406672631393728</v>
+        <v>0.9766628971545965</v>
       </c>
       <c r="E7" t="n">
-        <v>87.63</v>
+        <v>98.69</v>
       </c>
       <c r="F7" t="n">
-        <v>58.88</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[8, 7, 6, 0, 1]</t>
+          <t>[6, 7, 4, 7, 8]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9418033924640898</v>
+        <v>0.9684368298286937</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9418033924640898</v>
+        <v>0.9684368298286937</v>
       </c>
       <c r="E8" t="n">
-        <v>96.48</v>
+        <v>112.89</v>
       </c>
       <c r="F8" t="n">
-        <v>59.81</v>
+        <v>90.88999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[3, 1, 5, 4, 4]</t>
+          <t>[4, 1, 7, 4, 1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.954507752919182</v>
+        <v>0.9934454312059382</v>
       </c>
       <c r="D9" t="n">
-        <v>0.954507752919182</v>
+        <v>0.9934454312059382</v>
       </c>
       <c r="E9" t="n">
-        <v>79.20000000000002</v>
+        <v>110.54</v>
       </c>
       <c r="F9" t="n">
-        <v>73.95</v>
+        <v>97.08000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[4, 9, 9, 2, 9]</t>
+          <t>[2, 1, 7, 7, 4]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9385124775447717</v>
+        <v>0.9752559548773041</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9385124775447717</v>
+        <v>0.9752559548773041</v>
       </c>
       <c r="E10" t="n">
-        <v>87.59999999999999</v>
+        <v>102.37</v>
       </c>
       <c r="F10" t="n">
-        <v>76.88</v>
+        <v>91.43000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[2, 5, 2, 7, 5]</t>
+          <t>[3, 4, 6, 1, 4]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9429043266390494</v>
+        <v>0.9743180435652004</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9429043266390494</v>
+        <v>0.9743180435652004</v>
       </c>
       <c r="E11" t="n">
-        <v>95.56</v>
+        <v>115.13</v>
       </c>
       <c r="F11" t="n">
-        <v>70.36</v>
+        <v>95.23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[7, 9, 4, 6, 7]</t>
+          <t>[5, 6, 7, 0, 5]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9302865649093305</v>
+        <v>0.9676068836244485</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9302865649093305</v>
+        <v>0.9676068836244485</v>
       </c>
       <c r="E12" t="n">
-        <v>92.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="F12" t="n">
-        <v>61.76000000000001</v>
+        <v>86.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[6, 8, 9, 2, 5]</t>
+          <t>[7, 1, 7, 8, 6]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9335097458401305</v>
+        <v>0.9498550180150503</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9335097458401305</v>
+        <v>0.9498550180150503</v>
       </c>
       <c r="E13" t="n">
-        <v>94.27000000000001</v>
+        <v>94.09</v>
       </c>
       <c r="F13" t="n">
-        <v>70.52</v>
+        <v>79.69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[0, 4, 8, 1, 4]</t>
+          <t>[2, 7, 0, 5, 0]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9737345419578265</v>
+        <v>0.9755642197839086</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9737345419578265</v>
+        <v>0.9755642197839086</v>
       </c>
       <c r="E14" t="n">
-        <v>98.30000000000001</v>
+        <v>102.84</v>
       </c>
       <c r="F14" t="n">
-        <v>79.70999999999999</v>
+        <v>86.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[9, 8, 8, 8, 7]</t>
+          <t>[8, 5, 3, 5, 9]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9185926053994604</v>
+        <v>0.9667112501083031</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9185926053994604</v>
+        <v>0.9667112501083031</v>
       </c>
       <c r="E15" t="n">
-        <v>96.02000000000001</v>
+        <v>92.47</v>
       </c>
       <c r="F15" t="n">
-        <v>63.11</v>
+        <v>84.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[2, 4, 2, 8, 3]</t>
+          <t>[9, 7, 5, 3, 6]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9499543088097407</v>
+        <v>0.9628683675124132</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9499543088097407</v>
+        <v>0.9628683675124132</v>
       </c>
       <c r="E16" t="n">
-        <v>75.17</v>
+        <v>88.41999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>77.17</v>
+        <v>78.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[1, 7, 4, 4, 9]</t>
+          <t>[9, 5, 2, 5, 7]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9653393419182984</v>
+        <v>0.9669652225566107</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9653393419182984</v>
+        <v>0.9669652225566107</v>
       </c>
       <c r="E17" t="n">
-        <v>97.63000000000002</v>
+        <v>96.33999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>75.07000000000001</v>
+        <v>89.81999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[9, 5, 2, 2, 9]</t>
+          <t>[4, 5, 8, 9, 8]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9444370384942763</v>
+        <v>0.9625593328456</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9444370384942763</v>
+        <v>0.9625593328456</v>
       </c>
       <c r="E18" t="n">
-        <v>92.10999999999999</v>
+        <v>108.09</v>
       </c>
       <c r="F18" t="n">
-        <v>76.27000000000001</v>
+        <v>84.22999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[2, 6, 8, 1, 3]</t>
+          <t>[5, 1, 9, 6, 5]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9504001434301541</v>
+        <v>0.9645917986189821</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9504001434301541</v>
+        <v>0.9645917986189821</v>
       </c>
       <c r="E19" t="n">
-        <v>82.04000000000001</v>
+        <v>90.82000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>67.16000000000001</v>
+        <v>88.96000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[4, 6, 1, 6, 8]</t>
+          <t>[1, 8, 7, 6, 4]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9622293573688957</v>
+        <v>0.9914598393464963</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9622293573688957</v>
+        <v>0.9914598393464963</v>
       </c>
       <c r="E20" t="n">
-        <v>99.09999999999999</v>
+        <v>118.7</v>
       </c>
       <c r="F20" t="n">
-        <v>71.39</v>
+        <v>97.21000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[9, 7, 2, 9, 7]</t>
+          <t>[7, 1, 9, 7, 8]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9300559114565724</v>
+        <v>0.9625405760674843</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9300559114565724</v>
+        <v>0.9625405760674843</v>
       </c>
       <c r="E21" t="n">
-        <v>96.38</v>
+        <v>95.31</v>
       </c>
       <c r="F21" t="n">
-        <v>64.44</v>
+        <v>83.41999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[3, 5, 2, 1, 1]</t>
+          <t>[5, 0, 2, 1, 2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9765759891394756</v>
+        <v>0.9732739089902639</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9765759891394756</v>
+        <v>0.9732739089902639</v>
       </c>
       <c r="E22" t="n">
-        <v>99.45999999999999</v>
+        <v>113.47</v>
       </c>
       <c r="F22" t="n">
-        <v>76.15000000000001</v>
+        <v>96.19999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[9, 8, 8, 3, 0]</t>
+          <t>[7, 8, 6, 7, 2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9319550035027171</v>
+        <v>0.9870941433706616</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9319550035027171</v>
+        <v>0.9870941433706616</v>
       </c>
       <c r="E23" t="n">
-        <v>95.37</v>
+        <v>107.12</v>
       </c>
       <c r="F23" t="n">
-        <v>74.84</v>
+        <v>90.56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[9, 3, 1, 4, 6]</t>
+          <t>[8, 7, 2, 4, 5]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 2, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.972136838221531</v>
+        <v>0.9738432435012332</v>
       </c>
       <c r="D24" t="n">
-        <v>0.972136838221531</v>
+        <v>0.9738432435012332</v>
       </c>
       <c r="E24" t="n">
-        <v>97.72999999999999</v>
+        <v>112.95</v>
       </c>
       <c r="F24" t="n">
-        <v>79.38</v>
+        <v>94.63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[1, 0, 1, 5, 3]</t>
+          <t>[7, 7, 7, 8, 5]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9654962743850839</v>
+        <v>0.9662109964797775</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9654962743850839</v>
+        <v>0.9662109964797775</v>
       </c>
       <c r="E25" t="n">
-        <v>92.69</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>67.73999999999999</v>
+        <v>86.02000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[1, 5, 5, 9, 1]</t>
+          <t>[8, 7, 7, 0, 4]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 2]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9427288559368738</v>
+        <v>0.9740897361446375</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9427288559368738</v>
+        <v>0.9740897361446375</v>
       </c>
       <c r="E26" t="n">
-        <v>97.25</v>
+        <v>115.77</v>
       </c>
       <c r="F26" t="n">
-        <v>64.13</v>
+        <v>90.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[2, 1, 2, 4, 0]</t>
+          <t>[1, 3, 2, 1, 9]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9635970496550067</v>
+        <v>0.9762082686565305</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9635970496550067</v>
+        <v>0.9762082686565305</v>
       </c>
       <c r="E27" t="n">
-        <v>80.5</v>
+        <v>105.57</v>
       </c>
       <c r="F27" t="n">
-        <v>72.34</v>
+        <v>91.76000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[4, 3, 4, 9, 5]</t>
+          <t>[9, 6, 1, 1, 1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9448946285790429</v>
+        <v>0.9728543711301958</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9448946285790429</v>
+        <v>0.9728543711301958</v>
       </c>
       <c r="E28" t="n">
-        <v>83.73</v>
+        <v>100.7</v>
       </c>
       <c r="F28" t="n">
-        <v>79.8</v>
+        <v>90.87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[9, 7, 1, 7, 7]</t>
+          <t>[5, 8, 9, 3, 9]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9355089767453318</v>
+        <v>0.968658400972089</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9355089767453318</v>
+        <v>0.968658400972089</v>
       </c>
       <c r="E29" t="n">
-        <v>98.22999999999999</v>
+        <v>111.63</v>
       </c>
       <c r="F29" t="n">
-        <v>52.55000000000001</v>
+        <v>99.98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[2, 0, 7, 0, 4]</t>
+          <t>[1, 7, 4, 1, 3]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9592843549858047</v>
+        <v>0.9764658715897816</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9592843549858047</v>
+        <v>0.9764658715897816</v>
       </c>
       <c r="E30" t="n">
-        <v>94.55000000000001</v>
+        <v>110.91</v>
       </c>
       <c r="F30" t="n">
-        <v>73.27000000000001</v>
+        <v>93.13000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 3, 9]</t>
+          <t>[7, 1, 4, 6, 5]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 3, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9798206449177506</v>
+        <v>0.9718513835583928</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9798206449177506</v>
+        <v>0.9718513835583928</v>
       </c>
       <c r="E31" t="n">
-        <v>97.47</v>
+        <v>104.49</v>
       </c>
       <c r="F31" t="n">
-        <v>78.45</v>
+        <v>99.03</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[6, 1, 2, 9, 7]</t>
+          <t>[8, 3, 7, 7, 3]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9486412678354071</v>
+        <v>0.9702675267792542</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9486412678354071</v>
+        <v>0.9702675267792542</v>
       </c>
       <c r="E32" t="n">
-        <v>89.42999999999998</v>
+        <v>117.28</v>
       </c>
       <c r="F32" t="n">
-        <v>61.20999999999999</v>
+        <v>94.56000000000002</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[1, 5, 2, 1, 6]</t>
+          <t>[3, 9, 7, 4, 5]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9613592091799174</v>
+        <v>0.9657910416884156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9613592091799174</v>
+        <v>0.9657910416884156</v>
       </c>
       <c r="E33" t="n">
-        <v>87.00999999999999</v>
+        <v>89.27999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>61.15</v>
+        <v>77.50999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[3, 0, 8, 5, 3]</t>
+          <t>[6, 7, 8, 2, 7]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9492716799567813</v>
+        <v>0.9681919564868757</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9492716799567813</v>
+        <v>0.9681919564868757</v>
       </c>
       <c r="E34" t="n">
-        <v>95.03</v>
+        <v>114.87</v>
       </c>
       <c r="F34" t="n">
-        <v>79.54000000000001</v>
+        <v>96.01000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[3, 9, 0, 6, 2]</t>
+          <t>[7, 7, 0, 3, 7]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[3, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9461413291646518</v>
+        <v>0.9750945065918287</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9461413291646518</v>
+        <v>0.9750945065918287</v>
       </c>
       <c r="E35" t="n">
-        <v>91.50999999999999</v>
+        <v>112.75</v>
       </c>
       <c r="F35" t="n">
-        <v>76.46000000000001</v>
+        <v>96.63000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[3, 7, 1, 2, 7]</t>
+          <t>[7, 6, 2, 4, 7]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9538031377330007</v>
+        <v>0.9694847640561223</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9538031377330007</v>
+        <v>0.9694847640561223</v>
       </c>
       <c r="E36" t="n">
-        <v>86.93000000000001</v>
+        <v>91.32999999999998</v>
       </c>
       <c r="F36" t="n">
-        <v>61.02</v>
+        <v>78.07000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[1, 9, 2, 0, 0]</t>
+          <t>[3, 7, 5, 8, 7]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 2, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9615721294360728</v>
+        <v>0.9917185821690001</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9615721294360728</v>
+        <v>0.9917185821690001</v>
       </c>
       <c r="E37" t="n">
-        <v>96.78999999999999</v>
+        <v>113.92</v>
       </c>
       <c r="F37" t="n">
-        <v>72.53</v>
+        <v>97.55</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[7, 3, 3, 9, 9]</t>
+          <t>[8, 5, 6, 2, 3]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9380131835605816</v>
+        <v>0.9741307353640242</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9380131835605816</v>
+        <v>0.9741307353640242</v>
       </c>
       <c r="E38" t="n">
-        <v>91.58000000000001</v>
+        <v>118.7</v>
       </c>
       <c r="F38" t="n">
-        <v>74.95999999999999</v>
+        <v>97.79000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[8, 3, 6, 3, 9]</t>
+          <t>[3, 1, 3, 5, 3]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9391232965861246</v>
+        <v>0.973706732606733</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9391232965861246</v>
+        <v>0.973706732606733</v>
       </c>
       <c r="E39" t="n">
-        <v>87.35999999999999</v>
+        <v>90.05</v>
       </c>
       <c r="F39" t="n">
-        <v>75.25</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[4, 0, 6, 0, 4]</t>
+          <t>[7, 1, 8, 6, 5]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9584003717083389</v>
+        <v>0.9510424353141017</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9584003717083389</v>
+        <v>0.9510424353141017</v>
       </c>
       <c r="E40" t="n">
-        <v>90.40000000000001</v>
+        <v>101.92</v>
       </c>
       <c r="F40" t="n">
-        <v>76.44</v>
+        <v>98.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[8, 1, 4, 8, 1]</t>
+          <t>[4, 9, 8, 2, 7]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.966068286786232</v>
+        <v>0.9656070029501255</v>
       </c>
       <c r="D41" t="n">
-        <v>0.966068286786232</v>
+        <v>0.9656070029501255</v>
       </c>
       <c r="E41" t="n">
-        <v>96.27000000000001</v>
+        <v>107.46</v>
       </c>
       <c r="F41" t="n">
-        <v>69.67</v>
+        <v>84.09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[2, 6, 8, 3, 0]</t>
+          <t>[9, 8, 4, 1, 8]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9456763978004059</v>
+        <v>0.9660577878765254</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9456763978004059</v>
+        <v>0.9660577878765254</v>
       </c>
       <c r="E42" t="n">
-        <v>89.71000000000001</v>
+        <v>108.88</v>
       </c>
       <c r="F42" t="n">
-        <v>74.13000000000001</v>
+        <v>87.58000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[3, 2, 5, 0, 1]</t>
+          <t>[6, 7, 3, 9, 3]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9573910984071942</v>
+        <v>0.9715995903295306</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9573910984071942</v>
+        <v>0.9715995903295306</v>
       </c>
       <c r="E43" t="n">
-        <v>91.51000000000001</v>
+        <v>107.41</v>
       </c>
       <c r="F43" t="n">
-        <v>73.78</v>
+        <v>86.55</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[8, 1, 1, 6, 4]</t>
+          <t>[3, 6, 3, 9, 5]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 2, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9591564639322755</v>
+        <v>0.9772256607458221</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9591564639322755</v>
+        <v>0.9772256607458221</v>
       </c>
       <c r="E44" t="n">
-        <v>93.41</v>
+        <v>115.05</v>
       </c>
       <c r="F44" t="n">
-        <v>75.36</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[6, 9, 0, 1, 9]</t>
+          <t>[9, 9, 7, 3, 3]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9541442935647981</v>
+        <v>0.9692891379394266</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9541442935647981</v>
+        <v>0.9692891379394266</v>
       </c>
       <c r="E45" t="n">
-        <v>97.60999999999999</v>
+        <v>106.72</v>
       </c>
       <c r="F45" t="n">
-        <v>67.98999999999999</v>
+        <v>88.39000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[1, 6, 2, 1, 4]</t>
+          <t>[8, 4, 2, 4, 5]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9756948357781959</v>
+        <v>0.9536107813934506</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9756948357781959</v>
+        <v>0.9536107813934506</v>
       </c>
       <c r="E46" t="n">
-        <v>92.41</v>
+        <v>100.46</v>
       </c>
       <c r="F46" t="n">
-        <v>71.28999999999999</v>
+        <v>86.15000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[7, 1, 4, 6, 4]</t>
+          <t>[4, 3, 7, 7, 5]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[3, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9659659758939519</v>
+        <v>0.9918564500512252</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9659659758939519</v>
+        <v>0.9918564500512252</v>
       </c>
       <c r="E47" t="n">
-        <v>98.66</v>
+        <v>117.42</v>
       </c>
       <c r="F47" t="n">
-        <v>74.46000000000001</v>
+        <v>99.69</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[3, 6, 6, 3, 5]</t>
+          <t>[5, 5, 5, 1, 3]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9432209218230753</v>
+        <v>0.9712972507194235</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9432209218230753</v>
+        <v>0.9712972507194235</v>
       </c>
       <c r="E48" t="n">
-        <v>90.19</v>
+        <v>95.60000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>74.29000000000001</v>
+        <v>96.48</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[2, 3, 3, 7, 5]</t>
+          <t>[5, 7, 7, 5, 5]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9484473851847194</v>
+        <v>0.9657078131769495</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9484473851847194</v>
+        <v>0.9657078131769495</v>
       </c>
       <c r="E49" t="n">
-        <v>88.65000000000001</v>
+        <v>73.84</v>
       </c>
       <c r="F49" t="n">
-        <v>75.09</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[1, 7, 3, 3, 2]</t>
+          <t>[8, 1, 1, 9, 9]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9533329620918927</v>
+        <v>0.9681234236611707</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9533329620918927</v>
+        <v>0.9681234236611707</v>
       </c>
       <c r="E50" t="n">
-        <v>81.34</v>
+        <v>104.97</v>
       </c>
       <c r="F50" t="n">
-        <v>69.3</v>
+        <v>91.35000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[4, 1, 6, 8, 7]</t>
+          <t>[3, 4, 3, 1, 6]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.971717270211979</v>
+        <v>0.993896923399245</v>
       </c>
       <c r="D51" t="n">
-        <v>0.971717270211979</v>
+        <v>0.993896923399245</v>
       </c>
       <c r="E51" t="n">
-        <v>98.60999999999999</v>
+        <v>111.47</v>
       </c>
       <c r="F51" t="n">
-        <v>75.36000000000001</v>
+        <v>92.11</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_4.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_4.xlsx
@@ -463,31 +463,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[9, 7, 7, 4, 8]</t>
+          <t>[6, 1, 8, 9, 7]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[2, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.961069264612964</v>
+        <v>0.9736963143296997</v>
       </c>
       <c r="D2" t="n">
-        <v>0.961069264612964</v>
+        <v>0.9736963143296997</v>
       </c>
       <c r="E2" t="n">
-        <v>94.63000000000001</v>
+        <v>119.86</v>
       </c>
       <c r="F2" t="n">
-        <v>77.06</v>
+        <v>98.81999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[8, 0, 9, 6, 9]</t>
+          <t>[1, 6, 5, 7, 3]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -496,46 +496,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9603114227836372</v>
+        <v>0.9691028876229542</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9603114227836372</v>
+        <v>0.9691028876229542</v>
       </c>
       <c r="E3" t="n">
-        <v>115.23</v>
+        <v>103.3</v>
       </c>
       <c r="F3" t="n">
-        <v>88.33</v>
+        <v>79.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[7, 7, 8, 6, 7]</t>
+          <t>[2, 5, 1, 4, 0]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9626052054139339</v>
+        <v>0.9526731224931636</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9626052054139339</v>
+        <v>0.9526731224931636</v>
       </c>
       <c r="E4" t="n">
-        <v>86.99000000000001</v>
+        <v>99.58</v>
       </c>
       <c r="F4" t="n">
-        <v>73.61999999999999</v>
+        <v>64.69999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[1, 7, 3, 7, 6]</t>
+          <t>[4, 6, 1, 1, 7]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -544,262 +544,262 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.966918932696361</v>
+        <v>0.9724810286472328</v>
       </c>
       <c r="D5" t="n">
-        <v>0.966918932696361</v>
+        <v>0.9724810286472328</v>
       </c>
       <c r="E5" t="n">
-        <v>87.88</v>
+        <v>112.22</v>
       </c>
       <c r="F5" t="n">
-        <v>75.05</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[6, 4, 7, 0, 8]</t>
+          <t>[2, 1, 0, 5, 6]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 2, 2, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9895642721316892</v>
+        <v>0.9786009306132566</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9895642721316892</v>
+        <v>0.9786009306132566</v>
       </c>
       <c r="E6" t="n">
-        <v>119.99</v>
+        <v>113.95</v>
       </c>
       <c r="F6" t="n">
-        <v>92.96000000000001</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[1, 7, 1, 4, 8]</t>
+          <t>[7, 5, 8, 7, 5]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9766628971545965</v>
+        <v>0.9643673640588338</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9766628971545965</v>
+        <v>0.9643673640588338</v>
       </c>
       <c r="E7" t="n">
-        <v>98.69</v>
+        <v>116.53</v>
       </c>
       <c r="F7" t="n">
-        <v>82.62</v>
+        <v>94.58000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[6, 7, 4, 7, 8]</t>
+          <t>[6, 1, 8, 7, 7]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[3, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9684368298286937</v>
+        <v>0.9625232311006898</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9684368298286937</v>
+        <v>0.9625232311006898</v>
       </c>
       <c r="E8" t="n">
-        <v>112.89</v>
+        <v>99.10000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>90.88999999999999</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[4, 1, 7, 4, 1]</t>
+          <t>[5, 0, 8, 4, 5]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[2, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9934454312059382</v>
+        <v>0.9520380784682417</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9934454312059382</v>
+        <v>0.9520380784682417</v>
       </c>
       <c r="E9" t="n">
-        <v>110.54</v>
+        <v>102.79</v>
       </c>
       <c r="F9" t="n">
-        <v>97.08000000000001</v>
+        <v>74.43000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[2, 1, 7, 7, 4]</t>
+          <t>[6, 4, 7, 2, 1]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9752559548773041</v>
+        <v>0.9702582766436624</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9752559548773041</v>
+        <v>0.9702582766436624</v>
       </c>
       <c r="E10" t="n">
-        <v>102.37</v>
+        <v>118.77</v>
       </c>
       <c r="F10" t="n">
-        <v>91.43000000000001</v>
+        <v>77.86000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[3, 4, 6, 1, 4]</t>
+          <t>[5, 9, 1, 4, 1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9743180435652004</v>
+        <v>0.9707646482802651</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9743180435652004</v>
+        <v>0.9707646482802651</v>
       </c>
       <c r="E11" t="n">
-        <v>115.13</v>
+        <v>116.84</v>
       </c>
       <c r="F11" t="n">
-        <v>95.23</v>
+        <v>85.68000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[5, 6, 7, 0, 5]</t>
+          <t>[9, 1, 2, 9, 5]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9676068836244485</v>
+        <v>0.9443330220648412</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9676068836244485</v>
+        <v>0.9443330220648412</v>
       </c>
       <c r="E12" t="n">
-        <v>99.2</v>
+        <v>92.38000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>86.44</v>
+        <v>70.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[7, 1, 7, 8, 6]</t>
+          <t>[7, 8, 8, 3, 1]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9498550180150503</v>
+        <v>0.9377351569159873</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9498550180150503</v>
+        <v>0.9377351569159873</v>
       </c>
       <c r="E13" t="n">
-        <v>94.09</v>
+        <v>83.56</v>
       </c>
       <c r="F13" t="n">
-        <v>79.69</v>
+        <v>68.27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[2, 7, 0, 5, 0]</t>
+          <t>[5, 4, 4, 9, 1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9755642197839086</v>
+        <v>0.964644389191831</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9755642197839086</v>
+        <v>0.964644389191831</v>
       </c>
       <c r="E14" t="n">
-        <v>102.84</v>
+        <v>117.15</v>
       </c>
       <c r="F14" t="n">
-        <v>86.78</v>
+        <v>88.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[8, 5, 3, 5, 9]</t>
+          <t>[6, 8, 2, 9, 4]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9667112501083031</v>
+        <v>0.9590711990201085</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9667112501083031</v>
+        <v>0.9590711990201085</v>
       </c>
       <c r="E15" t="n">
-        <v>92.47</v>
+        <v>119.51</v>
       </c>
       <c r="F15" t="n">
-        <v>84.53</v>
+        <v>79.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[9, 7, 5, 3, 6]</t>
+          <t>[9, 1, 2, 3, 8]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -808,142 +808,142 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9628683675124132</v>
+        <v>0.9671864364545872</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9628683675124132</v>
+        <v>0.9671864364545872</v>
       </c>
       <c r="E16" t="n">
-        <v>88.41999999999999</v>
+        <v>114.07</v>
       </c>
       <c r="F16" t="n">
-        <v>78.03</v>
+        <v>82.11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[9, 5, 2, 5, 7]</t>
+          <t>[5, 0, 6, 7, 3]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9669652225566107</v>
+        <v>0.9649927631036374</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9669652225566107</v>
+        <v>0.9649927631036374</v>
       </c>
       <c r="E17" t="n">
-        <v>96.33999999999999</v>
+        <v>105.47</v>
       </c>
       <c r="F17" t="n">
-        <v>89.81999999999999</v>
+        <v>80.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[4, 5, 8, 9, 8]</t>
+          <t>[1, 6, 4, 4, 5]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9625593328456</v>
+        <v>0.9525212890587759</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9625593328456</v>
+        <v>0.9525212890587759</v>
       </c>
       <c r="E18" t="n">
-        <v>108.09</v>
+        <v>115.08</v>
       </c>
       <c r="F18" t="n">
-        <v>84.22999999999999</v>
+        <v>75.81999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[5, 1, 9, 6, 5]</t>
+          <t>[9, 2, 5, 8, 9]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9645917986189821</v>
+        <v>0.9654549038256524</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9645917986189821</v>
+        <v>0.9654549038256524</v>
       </c>
       <c r="E19" t="n">
-        <v>90.82000000000001</v>
+        <v>107.27</v>
       </c>
       <c r="F19" t="n">
-        <v>88.96000000000001</v>
+        <v>86.52000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[1, 8, 7, 6, 4]</t>
+          <t>[8, 6, 9, 8, 0]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[2, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9914598393464963</v>
+        <v>0.9367405985576411</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9914598393464963</v>
+        <v>0.9367405985576411</v>
       </c>
       <c r="E20" t="n">
-        <v>118.7</v>
+        <v>108.13</v>
       </c>
       <c r="F20" t="n">
-        <v>97.21000000000001</v>
+        <v>89.08</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[7, 1, 9, 7, 8]</t>
+          <t>[2, 8, 8, 0, 7]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9625405760674843</v>
+        <v>0.9564917271740383</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9625405760674843</v>
+        <v>0.9564917271740383</v>
       </c>
       <c r="E21" t="n">
-        <v>95.31</v>
+        <v>114.61</v>
       </c>
       <c r="F21" t="n">
-        <v>83.41999999999999</v>
+        <v>96.81999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[5, 0, 2, 1, 2]</t>
+          <t>[2, 3, 7, 1, 7]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -952,142 +952,142 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9732739089902639</v>
+        <v>0.9705077202286749</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9732739089902639</v>
+        <v>0.9705077202286749</v>
       </c>
       <c r="E22" t="n">
-        <v>113.47</v>
+        <v>113.43</v>
       </c>
       <c r="F22" t="n">
-        <v>96.19999999999999</v>
+        <v>77.88000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[7, 8, 6, 7, 2]</t>
+          <t>[7, 6, 5, 9, 7]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 2, 1]</t>
+          <t>[2, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9870941433706616</v>
+        <v>0.9880788645880979</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9870941433706616</v>
+        <v>0.9880788645880979</v>
       </c>
       <c r="E23" t="n">
-        <v>107.12</v>
+        <v>115.63</v>
       </c>
       <c r="F23" t="n">
-        <v>90.56</v>
+        <v>97.36000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[8, 7, 2, 4, 5]</t>
+          <t>[5, 5, 6, 7, 2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9738432435012332</v>
+        <v>0.9622296741802026</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9738432435012332</v>
+        <v>0.9622296741802026</v>
       </c>
       <c r="E24" t="n">
-        <v>112.95</v>
+        <v>101.09</v>
       </c>
       <c r="F24" t="n">
-        <v>94.63</v>
+        <v>67.63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[7, 7, 7, 8, 5]</t>
+          <t>[5, 6, 9, 2, 8]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9662109964797775</v>
+        <v>0.9385688117132045</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9662109964797775</v>
+        <v>0.9385688117132045</v>
       </c>
       <c r="E25" t="n">
-        <v>95.04000000000001</v>
+        <v>90.47</v>
       </c>
       <c r="F25" t="n">
-        <v>86.02000000000001</v>
+        <v>63.31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[8, 7, 7, 0, 4]</t>
+          <t>[9, 6, 2, 0, 9]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 2]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9740897361446375</v>
+        <v>0.9723576589532559</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9740897361446375</v>
+        <v>0.9723576589532559</v>
       </c>
       <c r="E26" t="n">
-        <v>115.77</v>
+        <v>118.25</v>
       </c>
       <c r="F26" t="n">
-        <v>90.86</v>
+        <v>91.34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[1, 3, 2, 1, 9]</t>
+          <t>[8, 8, 4, 5, 2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9762082686565305</v>
+        <v>0.986178163429797</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9762082686565305</v>
+        <v>0.986178163429797</v>
       </c>
       <c r="E27" t="n">
-        <v>105.57</v>
+        <v>119.68</v>
       </c>
       <c r="F27" t="n">
-        <v>91.76000000000001</v>
+        <v>84.19999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[9, 6, 1, 1, 1]</t>
+          <t>[5, 6, 5, 8, 8]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1096,568 +1096,568 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9728543711301958</v>
+        <v>0.9601638313573307</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9728543711301958</v>
+        <v>0.9601638313573307</v>
       </c>
       <c r="E28" t="n">
-        <v>100.7</v>
+        <v>93.37</v>
       </c>
       <c r="F28" t="n">
-        <v>90.87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[5, 8, 9, 3, 9]</t>
+          <t>[7, 4, 6, 4, 8]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[3, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.968658400972089</v>
+        <v>0.9624625796603615</v>
       </c>
       <c r="D29" t="n">
-        <v>0.968658400972089</v>
+        <v>0.9624625796603615</v>
       </c>
       <c r="E29" t="n">
-        <v>111.63</v>
+        <v>120</v>
       </c>
       <c r="F29" t="n">
-        <v>99.98</v>
+        <v>82.67999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[1, 7, 4, 1, 3]</t>
+          <t>[8, 0, 4, 6, 7]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9764658715897816</v>
+        <v>0.9721918049535371</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9764658715897816</v>
+        <v>0.9721918049535371</v>
       </c>
       <c r="E30" t="n">
-        <v>110.91</v>
+        <v>116.52</v>
       </c>
       <c r="F30" t="n">
-        <v>93.13000000000001</v>
+        <v>84.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[7, 1, 4, 6, 5]</t>
+          <t>[6, 0, 1, 5, 5]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 3, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9718513835583928</v>
+        <v>0.9741302467035655</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9718513835583928</v>
+        <v>0.9741302467035655</v>
       </c>
       <c r="E31" t="n">
-        <v>104.49</v>
+        <v>105.95</v>
       </c>
       <c r="F31" t="n">
-        <v>99.03</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[8, 3, 7, 7, 3]</t>
+          <t>[0, 2, 6, 8, 6]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 3, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9702675267792542</v>
+        <v>0.9692790755179275</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9702675267792542</v>
+        <v>0.9692790755179275</v>
       </c>
       <c r="E32" t="n">
-        <v>117.28</v>
+        <v>117.64</v>
       </c>
       <c r="F32" t="n">
-        <v>94.56000000000002</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[3, 9, 7, 4, 5]</t>
+          <t>[5, 0, 9, 7, 5]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 2, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9657910416884156</v>
+        <v>0.9652881899865167</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9657910416884156</v>
+        <v>0.9652881899865167</v>
       </c>
       <c r="E33" t="n">
-        <v>89.27999999999999</v>
+        <v>117.29</v>
       </c>
       <c r="F33" t="n">
-        <v>77.50999999999999</v>
+        <v>95.78</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[6, 7, 8, 2, 7]</t>
+          <t>[6, 4, 5, 5, 8]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9681919564868757</v>
+        <v>0.9621185722820014</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9681919564868757</v>
+        <v>0.9621185722820014</v>
       </c>
       <c r="E34" t="n">
-        <v>114.87</v>
+        <v>102.54</v>
       </c>
       <c r="F34" t="n">
-        <v>96.01000000000001</v>
+        <v>70.69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[7, 7, 0, 3, 7]</t>
+          <t>[0, 1, 8, 4, 0]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[3, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9750945065918287</v>
+        <v>0.9575412150394215</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9750945065918287</v>
+        <v>0.9575412150394215</v>
       </c>
       <c r="E35" t="n">
-        <v>112.75</v>
+        <v>96.97</v>
       </c>
       <c r="F35" t="n">
-        <v>96.63000000000001</v>
+        <v>74.36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[7, 6, 2, 4, 7]</t>
+          <t>[1, 5, 9, 8, 5]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9694847640561223</v>
+        <v>0.9398616021808605</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9694847640561223</v>
+        <v>0.9398616021808605</v>
       </c>
       <c r="E36" t="n">
-        <v>91.32999999999998</v>
+        <v>80.55</v>
       </c>
       <c r="F36" t="n">
-        <v>78.07000000000001</v>
+        <v>66.51000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[3, 7, 5, 8, 7]</t>
+          <t>[4, 8, 0, 5, 5]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[2, 2, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9917185821690001</v>
+        <v>0.9473430044053406</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9917185821690001</v>
+        <v>0.9473430044053406</v>
       </c>
       <c r="E37" t="n">
-        <v>113.92</v>
+        <v>88.06</v>
       </c>
       <c r="F37" t="n">
-        <v>97.55</v>
+        <v>64.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[8, 5, 6, 2, 3]</t>
+          <t>[5, 8, 6, 9, 7]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 2, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9741307353640242</v>
+        <v>0.968352545164849</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9741307353640242</v>
+        <v>0.968352545164849</v>
       </c>
       <c r="E38" t="n">
-        <v>118.7</v>
+        <v>114.88</v>
       </c>
       <c r="F38" t="n">
-        <v>97.79000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[3, 1, 3, 5, 3]</t>
+          <t>[8, 9, 6, 8, 4]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.973706732606733</v>
+        <v>0.9593031757692221</v>
       </c>
       <c r="D39" t="n">
-        <v>0.973706732606733</v>
+        <v>0.9593031757692221</v>
       </c>
       <c r="E39" t="n">
-        <v>90.05</v>
+        <v>105.92</v>
       </c>
       <c r="F39" t="n">
-        <v>76</v>
+        <v>84.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[7, 1, 8, 6, 5]</t>
+          <t>[9, 3, 5, 6, 4]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 3]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9510424353141017</v>
+        <v>0.9363830143229754</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9510424353141017</v>
+        <v>0.9363830143229754</v>
       </c>
       <c r="E40" t="n">
-        <v>101.92</v>
+        <v>99.06</v>
       </c>
       <c r="F40" t="n">
-        <v>98.11</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[4, 9, 8, 2, 7]</t>
+          <t>[8, 2, 8, 8, 2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[2, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9656070029501255</v>
+        <v>0.9735464413603105</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9656070029501255</v>
+        <v>0.9735464413603105</v>
       </c>
       <c r="E41" t="n">
-        <v>107.46</v>
+        <v>118.36</v>
       </c>
       <c r="F41" t="n">
-        <v>84.09</v>
+        <v>85.72999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[9, 8, 4, 1, 8]</t>
+          <t>[5, 7, 1, 6, 1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9660577878765254</v>
+        <v>0.9728236618703716</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9660577878765254</v>
+        <v>0.9728236618703716</v>
       </c>
       <c r="E42" t="n">
-        <v>108.88</v>
+        <v>117.35</v>
       </c>
       <c r="F42" t="n">
-        <v>87.58000000000001</v>
+        <v>96.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[6, 7, 3, 9, 3]</t>
+          <t>[7, 8, 9, 6, 7]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9715995903295306</v>
+        <v>0.9370240056972431</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9715995903295306</v>
+        <v>0.9370240056972431</v>
       </c>
       <c r="E43" t="n">
-        <v>107.41</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>86.55</v>
+        <v>88.03</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[3, 6, 3, 9, 5]</t>
+          <t>[6, 6, 5, 2, 2]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 2, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9772256607458221</v>
+        <v>0.9688184151988739</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9772256607458221</v>
+        <v>0.9688184151988739</v>
       </c>
       <c r="E44" t="n">
-        <v>115.05</v>
+        <v>114.96</v>
       </c>
       <c r="F44" t="n">
-        <v>95.59999999999999</v>
+        <v>64.34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[9, 9, 7, 3, 3]</t>
+          <t>[8, 4, 4, 7, 1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9692891379394266</v>
+        <v>0.9448972385356822</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9692891379394266</v>
+        <v>0.9448972385356822</v>
       </c>
       <c r="E45" t="n">
-        <v>106.72</v>
+        <v>112.43</v>
       </c>
       <c r="F45" t="n">
-        <v>88.39000000000001</v>
+        <v>85.77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[8, 4, 2, 4, 5]</t>
+          <t>[5, 2, 8, 4, 6]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9536107813934506</v>
+        <v>0.9694278170879004</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9536107813934506</v>
+        <v>0.9694278170879004</v>
       </c>
       <c r="E46" t="n">
-        <v>100.46</v>
+        <v>110.54</v>
       </c>
       <c r="F46" t="n">
-        <v>86.15000000000001</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[4, 3, 7, 7, 5]</t>
+          <t>[9, 0, 5, 7, 1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[3, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9918564500512252</v>
+        <v>0.9624402713901237</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9918564500512252</v>
+        <v>0.9624402713901237</v>
       </c>
       <c r="E47" t="n">
-        <v>117.42</v>
+        <v>105.93</v>
       </c>
       <c r="F47" t="n">
-        <v>99.69</v>
+        <v>89.91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 1, 3]</t>
+          <t>[5, 4, 8, 7, 4]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 2]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9712972507194235</v>
+        <v>0.9859249105067773</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9712972507194235</v>
+        <v>0.9859249105067773</v>
       </c>
       <c r="E48" t="n">
-        <v>95.60000000000001</v>
+        <v>119.84</v>
       </c>
       <c r="F48" t="n">
-        <v>96.48</v>
+        <v>91.72999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[5, 7, 7, 5, 5]</t>
+          <t>[9, 8, 7, 6, 0]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9657078131769495</v>
+        <v>0.9606602812885036</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9657078131769495</v>
+        <v>0.9606602812885036</v>
       </c>
       <c r="E49" t="n">
-        <v>73.84</v>
+        <v>105.84</v>
       </c>
       <c r="F49" t="n">
-        <v>80.98</v>
+        <v>92.25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[8, 1, 1, 9, 9]</t>
+          <t>[7, 7, 8, 6, 8]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9681234236611707</v>
+        <v>0.964640741779703</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9681234236611707</v>
+        <v>0.964640741779703</v>
       </c>
       <c r="E50" t="n">
-        <v>104.97</v>
+        <v>106.21</v>
       </c>
       <c r="F50" t="n">
-        <v>91.35000000000001</v>
+        <v>96.94</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[3, 4, 3, 1, 6]</t>
+          <t>[1, 7, 5, 8, 8]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 2, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.993896923399245</v>
+        <v>0.9867362469912182</v>
       </c>
       <c r="D51" t="n">
-        <v>0.993896923399245</v>
+        <v>0.9867362469912182</v>
       </c>
       <c r="E51" t="n">
-        <v>111.47</v>
+        <v>108.82</v>
       </c>
       <c r="F51" t="n">
-        <v>92.11</v>
+        <v>94.7</v>
       </c>
     </row>
   </sheetData>
